--- a/secretstockalerts.xlsx
+++ b/secretstockalerts.xlsx
@@ -390,7 +390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A676"/>
+  <dimension ref="A1:A677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -403,4725 +403,4732 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AB</t>
+          <t>https://www.secretstockalerts.com/aa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AC</t>
+          <t>https://www.secretstockalerts.com/ab</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AD</t>
+          <t>https://www.secretstockalerts.com/ac</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AE</t>
+          <t>https://www.secretstockalerts.com/ad</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AF</t>
+          <t>https://www.secretstockalerts.com/ae</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AG</t>
+          <t>https://www.secretstockalerts.com/af</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AH</t>
+          <t>https://www.secretstockalerts.com/ag</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AI</t>
+          <t>https://www.secretstockalerts.com/ah</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AJ</t>
+          <t>https://www.secretstockalerts.com/ai</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AK</t>
+          <t>https://www.secretstockalerts.com/aj</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AL</t>
+          <t>https://www.secretstockalerts.com/ak</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AM</t>
+          <t>https://www.secretstockalerts.com/al</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AN</t>
+          <t>https://www.secretstockalerts.com/am</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AO</t>
+          <t>https://www.secretstockalerts.com/an</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AP</t>
+          <t>https://www.secretstockalerts.com/ao</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AQ</t>
+          <t>https://www.secretstockalerts.com/ap</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AR</t>
+          <t>https://www.secretstockalerts.com/aq</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AS</t>
+          <t>https://www.secretstockalerts.com/ar</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AT</t>
+          <t>https://www.secretstockalerts.com/as</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AU</t>
+          <t>https://www.secretstockalerts.com/at</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AV</t>
+          <t>https://www.secretstockalerts.com/au</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AW</t>
+          <t>https://www.secretstockalerts.com/av</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AX</t>
+          <t>https://www.secretstockalerts.com/aw</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AY</t>
+          <t>https://www.secretstockalerts.com/ax</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/AZ</t>
+          <t>https://www.secretstockalerts.com/ay</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BA</t>
+          <t>https://www.secretstockalerts.com/az</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BB</t>
+          <t>https://www.secretstockalerts.com/ba</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BC</t>
+          <t>https://www.secretstockalerts.com/bb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BD</t>
+          <t>https://www.secretstockalerts.com/bc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BE</t>
+          <t>https://www.secretstockalerts.com/bd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BF</t>
+          <t>https://www.secretstockalerts.com/be</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BG</t>
+          <t>https://www.secretstockalerts.com/bf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BH</t>
+          <t>https://www.secretstockalerts.com/bg</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BI</t>
+          <t>https://www.secretstockalerts.com/bh</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BJ</t>
+          <t>https://www.secretstockalerts.com/bi</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BK</t>
+          <t>https://www.secretstockalerts.com/bj</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BL</t>
+          <t>https://www.secretstockalerts.com/bk</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BM</t>
+          <t>https://www.secretstockalerts.com/bl</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BN</t>
+          <t>https://www.secretstockalerts.com/bm</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BO</t>
+          <t>https://www.secretstockalerts.com/bn</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BP</t>
+          <t>https://www.secretstockalerts.com/bo</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BQ</t>
+          <t>https://www.secretstockalerts.com/bp</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BR</t>
+          <t>https://www.secretstockalerts.com/bq</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BS</t>
+          <t>https://www.secretstockalerts.com/br</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BT</t>
+          <t>https://www.secretstockalerts.com/bs</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BU</t>
+          <t>https://www.secretstockalerts.com/bt</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BV</t>
+          <t>https://www.secretstockalerts.com/bu</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BW</t>
+          <t>https://www.secretstockalerts.com/bv</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BX</t>
+          <t>https://www.secretstockalerts.com/bw</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BY</t>
+          <t>https://www.secretstockalerts.com/bx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/BZ</t>
+          <t>https://www.secretstockalerts.com/by</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CA</t>
+          <t>https://www.secretstockalerts.com/bz</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CB</t>
+          <t>https://www.secretstockalerts.com/ca</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CC</t>
+          <t>https://www.secretstockalerts.com/cb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CD</t>
+          <t>https://www.secretstockalerts.com/cc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CE</t>
+          <t>https://www.secretstockalerts.com/cd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CF</t>
+          <t>https://www.secretstockalerts.com/ce</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CG</t>
+          <t>https://www.secretstockalerts.com/cf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CH</t>
+          <t>https://www.secretstockalerts.com/cg</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CI</t>
+          <t>https://www.secretstockalerts.com/ch</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CJ</t>
+          <t>https://www.secretstockalerts.com/ci</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CK</t>
+          <t>https://www.secretstockalerts.com/cj</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CL</t>
+          <t>https://www.secretstockalerts.com/ck</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CM</t>
+          <t>https://www.secretstockalerts.com/cl</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CN</t>
+          <t>https://www.secretstockalerts.com/cm</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CO</t>
+          <t>https://www.secretstockalerts.com/cn</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CP</t>
+          <t>https://www.secretstockalerts.com/co</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CQ</t>
+          <t>https://www.secretstockalerts.com/cp</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CR</t>
+          <t>https://www.secretstockalerts.com/cq</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CS</t>
+          <t>https://www.secretstockalerts.com/cr</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CT</t>
+          <t>https://www.secretstockalerts.com/cs</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CU</t>
+          <t>https://www.secretstockalerts.com/ct</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CV</t>
+          <t>https://www.secretstockalerts.com/cu</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CW</t>
+          <t>https://www.secretstockalerts.com/cv</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CX</t>
+          <t>https://www.secretstockalerts.com/cw</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CY</t>
+          <t>https://www.secretstockalerts.com/cx</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/CZ</t>
+          <t>https://www.secretstockalerts.com/cy</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DA</t>
+          <t>https://www.secretstockalerts.com/cz</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DB</t>
+          <t>https://www.secretstockalerts.com/da</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DC</t>
+          <t>https://www.secretstockalerts.com/db</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DD</t>
+          <t>https://www.secretstockalerts.com/dc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DE</t>
+          <t>https://www.secretstockalerts.com/dd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DF</t>
+          <t>https://www.secretstockalerts.com/de</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DG</t>
+          <t>https://www.secretstockalerts.com/df</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DH</t>
+          <t>https://www.secretstockalerts.com/dg</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DI</t>
+          <t>https://www.secretstockalerts.com/dh</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DJ</t>
+          <t>https://www.secretstockalerts.com/di</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DK</t>
+          <t>https://www.secretstockalerts.com/dj</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DL</t>
+          <t>https://www.secretstockalerts.com/dk</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DM</t>
+          <t>https://www.secretstockalerts.com/dl</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DN</t>
+          <t>https://www.secretstockalerts.com/dm</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DO</t>
+          <t>https://www.secretstockalerts.com/dn</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DP</t>
+          <t>https://www.secretstockalerts.com/do</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DQ</t>
+          <t>https://www.secretstockalerts.com/dp</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DR</t>
+          <t>https://www.secretstockalerts.com/dq</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DS</t>
+          <t>https://www.secretstockalerts.com/dr</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DT</t>
+          <t>https://www.secretstockalerts.com/ds</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DU</t>
+          <t>https://www.secretstockalerts.com/dt</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DV</t>
+          <t>https://www.secretstockalerts.com/du</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DW</t>
+          <t>https://www.secretstockalerts.com/dv</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DX</t>
+          <t>https://www.secretstockalerts.com/dw</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DY</t>
+          <t>https://www.secretstockalerts.com/dx</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/DZ</t>
+          <t>https://www.secretstockalerts.com/dy</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EA</t>
+          <t>https://www.secretstockalerts.com/dz</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EB</t>
+          <t>https://www.secretstockalerts.com/ea</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EC</t>
+          <t>https://www.secretstockalerts.com/eb</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ED</t>
+          <t>https://www.secretstockalerts.com/ec</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EE</t>
+          <t>https://www.secretstockalerts.com/ed</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EF</t>
+          <t>https://www.secretstockalerts.com/ee</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EG</t>
+          <t>https://www.secretstockalerts.com/ef</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EH</t>
+          <t>https://www.secretstockalerts.com/eg</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EI</t>
+          <t>https://www.secretstockalerts.com/eh</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EJ</t>
+          <t>https://www.secretstockalerts.com/ei</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EK</t>
+          <t>https://www.secretstockalerts.com/ej</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EL</t>
+          <t>https://www.secretstockalerts.com/ek</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EM</t>
+          <t>https://www.secretstockalerts.com/el</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EN</t>
+          <t>https://www.secretstockalerts.com/em</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EO</t>
+          <t>https://www.secretstockalerts.com/en</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EP</t>
+          <t>https://www.secretstockalerts.com/eo</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EQ</t>
+          <t>https://www.secretstockalerts.com/ep</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ER</t>
+          <t>https://www.secretstockalerts.com/eq</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ES</t>
+          <t>https://www.secretstockalerts.com/er</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ET</t>
+          <t>https://www.secretstockalerts.com/es</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EU</t>
+          <t>https://www.secretstockalerts.com/et</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EV</t>
+          <t>https://www.secretstockalerts.com/eu</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EW</t>
+          <t>https://www.secretstockalerts.com/ev</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EX</t>
+          <t>https://www.secretstockalerts.com/ew</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EY</t>
+          <t>https://www.secretstockalerts.com/ex</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/EZ</t>
+          <t>https://www.secretstockalerts.com/ey</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FA</t>
+          <t>https://www.secretstockalerts.com/ez</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FB</t>
+          <t>https://www.secretstockalerts.com/fa</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FC</t>
+          <t>https://www.secretstockalerts.com/fb</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FD</t>
+          <t>https://www.secretstockalerts.com/fc</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FE</t>
+          <t>https://www.secretstockalerts.com/fd</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FF</t>
+          <t>https://www.secretstockalerts.com/fe</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FG</t>
+          <t>https://www.secretstockalerts.com/ff</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FH</t>
+          <t>https://www.secretstockalerts.com/fg</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FI</t>
+          <t>https://www.secretstockalerts.com/fh</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FJ</t>
+          <t>https://www.secretstockalerts.com/fi</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FK</t>
+          <t>https://www.secretstockalerts.com/fj</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FL</t>
+          <t>https://www.secretstockalerts.com/fk</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FM</t>
+          <t>https://www.secretstockalerts.com/fl</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FN</t>
+          <t>https://www.secretstockalerts.com/fm</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FO</t>
+          <t>https://www.secretstockalerts.com/fn</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FP</t>
+          <t>https://www.secretstockalerts.com/fo</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FQ</t>
+          <t>https://www.secretstockalerts.com/fp</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FR</t>
+          <t>https://www.secretstockalerts.com/fq</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FS</t>
+          <t>https://www.secretstockalerts.com/fr</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FT</t>
+          <t>https://www.secretstockalerts.com/fs</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FU</t>
+          <t>https://www.secretstockalerts.com/ft</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FV</t>
+          <t>https://www.secretstockalerts.com/fu</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FW</t>
+          <t>https://www.secretstockalerts.com/fv</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FX</t>
+          <t>https://www.secretstockalerts.com/fw</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FY</t>
+          <t>https://www.secretstockalerts.com/fx</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/FZ</t>
+          <t>https://www.secretstockalerts.com/fy</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GA</t>
+          <t>https://www.secretstockalerts.com/fz</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GB</t>
+          <t>https://www.secretstockalerts.com/ga</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GC</t>
+          <t>https://www.secretstockalerts.com/gb</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GD</t>
+          <t>https://www.secretstockalerts.com/gc</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GE</t>
+          <t>https://www.secretstockalerts.com/gd</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GF</t>
+          <t>https://www.secretstockalerts.com/ge</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GG</t>
+          <t>https://www.secretstockalerts.com/gf</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GH</t>
+          <t>https://www.secretstockalerts.com/gg</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GI</t>
+          <t>https://www.secretstockalerts.com/gh</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GJ</t>
+          <t>https://www.secretstockalerts.com/gi</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GK</t>
+          <t>https://www.secretstockalerts.com/gj</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GL</t>
+          <t>https://www.secretstockalerts.com/gk</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GM</t>
+          <t>https://www.secretstockalerts.com/gl</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GN</t>
+          <t>https://www.secretstockalerts.com/gm</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GO</t>
+          <t>https://www.secretstockalerts.com/gn</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GP</t>
+          <t>https://www.secretstockalerts.com/go</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GQ</t>
+          <t>https://www.secretstockalerts.com/gp</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GR</t>
+          <t>https://www.secretstockalerts.com/gq</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GS</t>
+          <t>https://www.secretstockalerts.com/gr</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GT</t>
+          <t>https://www.secretstockalerts.com/gs</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GU</t>
+          <t>https://www.secretstockalerts.com/gt</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GV</t>
+          <t>https://www.secretstockalerts.com/gu</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GW</t>
+          <t>https://www.secretstockalerts.com/gv</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GX</t>
+          <t>https://www.secretstockalerts.com/gw</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GY</t>
+          <t>https://www.secretstockalerts.com/gx</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/GZ</t>
+          <t>https://www.secretstockalerts.com/gy</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HA</t>
+          <t>https://www.secretstockalerts.com/gz</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HB</t>
+          <t>https://www.secretstockalerts.com/ha</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HC</t>
+          <t>https://www.secretstockalerts.com/hb</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HD</t>
+          <t>https://www.secretstockalerts.com/hc</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HE</t>
+          <t>https://www.secretstockalerts.com/hd</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HF</t>
+          <t>https://www.secretstockalerts.com/he</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HG</t>
+          <t>https://www.secretstockalerts.com/hf</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HH</t>
+          <t>https://www.secretstockalerts.com/hg</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HI</t>
+          <t>https://www.secretstockalerts.com/hh</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HJ</t>
+          <t>https://www.secretstockalerts.com/hi</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HK</t>
+          <t>https://www.secretstockalerts.com/hj</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HL</t>
+          <t>https://www.secretstockalerts.com/hk</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HM</t>
+          <t>https://www.secretstockalerts.com/hl</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HN</t>
+          <t>https://www.secretstockalerts.com/hm</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HO</t>
+          <t>https://www.secretstockalerts.com/hn</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HP</t>
+          <t>https://www.secretstockalerts.com/ho</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HQ</t>
+          <t>https://www.secretstockalerts.com/hp</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HR</t>
+          <t>https://www.secretstockalerts.com/hq</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HS</t>
+          <t>https://www.secretstockalerts.com/hr</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HT</t>
+          <t>https://www.secretstockalerts.com/hs</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HU</t>
+          <t>https://www.secretstockalerts.com/ht</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HV</t>
+          <t>https://www.secretstockalerts.com/hu</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HW</t>
+          <t>https://www.secretstockalerts.com/hv</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HX</t>
+          <t>https://www.secretstockalerts.com/hw</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HY</t>
+          <t>https://www.secretstockalerts.com/hx</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/HZ</t>
+          <t>https://www.secretstockalerts.com/hy</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IA</t>
+          <t>https://www.secretstockalerts.com/hz</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IB</t>
+          <t>https://www.secretstockalerts.com/ia</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IC</t>
+          <t>https://www.secretstockalerts.com/ib</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ID</t>
+          <t>https://www.secretstockalerts.com/ic</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IE</t>
+          <t>https://www.secretstockalerts.com/id</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IF</t>
+          <t>https://www.secretstockalerts.com/ie</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IG</t>
+          <t>https://www.secretstockalerts.com/if</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IH</t>
+          <t>https://www.secretstockalerts.com/ig</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/II</t>
+          <t>https://www.secretstockalerts.com/ih</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IJ</t>
+          <t>https://www.secretstockalerts.com/ii</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IK</t>
+          <t>https://www.secretstockalerts.com/ij</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IL</t>
+          <t>https://www.secretstockalerts.com/ik</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IM</t>
+          <t>https://www.secretstockalerts.com/il</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IN</t>
+          <t>https://www.secretstockalerts.com/im</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IO</t>
+          <t>https://www.secretstockalerts.com/in</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IP</t>
+          <t>https://www.secretstockalerts.com/io</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IQ</t>
+          <t>https://www.secretstockalerts.com/ip</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IR</t>
+          <t>https://www.secretstockalerts.com/iq</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IS</t>
+          <t>https://www.secretstockalerts.com/ir</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IT</t>
+          <t>https://www.secretstockalerts.com/is</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IU</t>
+          <t>https://www.secretstockalerts.com/it</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IV</t>
+          <t>https://www.secretstockalerts.com/iu</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IW</t>
+          <t>https://www.secretstockalerts.com/iv</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IX</t>
+          <t>https://www.secretstockalerts.com/iw</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IY</t>
+          <t>https://www.secretstockalerts.com/ix</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/IZ</t>
+          <t>https://www.secretstockalerts.com/iy</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JA</t>
+          <t>https://www.secretstockalerts.com/iz</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JB</t>
+          <t>https://www.secretstockalerts.com/ja</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JC</t>
+          <t>https://www.secretstockalerts.com/jb</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JD</t>
+          <t>https://www.secretstockalerts.com/jc</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JE</t>
+          <t>https://www.secretstockalerts.com/jd</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JF</t>
+          <t>https://www.secretstockalerts.com/je</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JG</t>
+          <t>https://www.secretstockalerts.com/jf</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JH</t>
+          <t>https://www.secretstockalerts.com/jg</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JI</t>
+          <t>https://www.secretstockalerts.com/jh</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JJ</t>
+          <t>https://www.secretstockalerts.com/ji</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JK</t>
+          <t>https://www.secretstockalerts.com/jj</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JL</t>
+          <t>https://www.secretstockalerts.com/jk</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JM</t>
+          <t>https://www.secretstockalerts.com/jl</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JN</t>
+          <t>https://www.secretstockalerts.com/jm</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JO</t>
+          <t>https://www.secretstockalerts.com/jn</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JP</t>
+          <t>https://www.secretstockalerts.com/jo</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JQ</t>
+          <t>https://www.secretstockalerts.com/jp</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JR</t>
+          <t>https://www.secretstockalerts.com/jq</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JS</t>
+          <t>https://www.secretstockalerts.com/jr</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JT</t>
+          <t>https://www.secretstockalerts.com/js</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JU</t>
+          <t>https://www.secretstockalerts.com/jt</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JV</t>
+          <t>https://www.secretstockalerts.com/ju</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JW</t>
+          <t>https://www.secretstockalerts.com/jv</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JX</t>
+          <t>https://www.secretstockalerts.com/jw</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JY</t>
+          <t>https://www.secretstockalerts.com/jx</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/JZ</t>
+          <t>https://www.secretstockalerts.com/jy</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KA</t>
+          <t>https://www.secretstockalerts.com/jz</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KB</t>
+          <t>https://www.secretstockalerts.com/ka</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KC</t>
+          <t>https://www.secretstockalerts.com/kb</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KD</t>
+          <t>https://www.secretstockalerts.com/kc</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KE</t>
+          <t>https://www.secretstockalerts.com/kd</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KF</t>
+          <t>https://www.secretstockalerts.com/ke</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KG</t>
+          <t>https://www.secretstockalerts.com/kf</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KH</t>
+          <t>https://www.secretstockalerts.com/kg</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KI</t>
+          <t>https://www.secretstockalerts.com/kh</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KJ</t>
+          <t>https://www.secretstockalerts.com/ki</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KK</t>
+          <t>https://www.secretstockalerts.com/kj</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KL</t>
+          <t>https://www.secretstockalerts.com/kk</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KM</t>
+          <t>https://www.secretstockalerts.com/kl</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KN</t>
+          <t>https://www.secretstockalerts.com/km</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KO</t>
+          <t>https://www.secretstockalerts.com/kn</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KP</t>
+          <t>https://www.secretstockalerts.com/ko</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KQ</t>
+          <t>https://www.secretstockalerts.com/kp</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KR</t>
+          <t>https://www.secretstockalerts.com/kq</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KS</t>
+          <t>https://www.secretstockalerts.com/kr</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KT</t>
+          <t>https://www.secretstockalerts.com/ks</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KU</t>
+          <t>https://www.secretstockalerts.com/kt</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KV</t>
+          <t>https://www.secretstockalerts.com/ku</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KW</t>
+          <t>https://www.secretstockalerts.com/kv</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KX</t>
+          <t>https://www.secretstockalerts.com/kw</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KY</t>
+          <t>https://www.secretstockalerts.com/kx</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/KZ</t>
+          <t>https://www.secretstockalerts.com/ky</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LA</t>
+          <t>https://www.secretstockalerts.com/kz</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LB</t>
+          <t>https://www.secretstockalerts.com/la</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LC</t>
+          <t>https://www.secretstockalerts.com/lb</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LD</t>
+          <t>https://www.secretstockalerts.com/lc</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LE</t>
+          <t>https://www.secretstockalerts.com/ld</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LF</t>
+          <t>https://www.secretstockalerts.com/le</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LG</t>
+          <t>https://www.secretstockalerts.com/lf</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LH</t>
+          <t>https://www.secretstockalerts.com/lg</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LI</t>
+          <t>https://www.secretstockalerts.com/lh</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LJ</t>
+          <t>https://www.secretstockalerts.com/li</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LK</t>
+          <t>https://www.secretstockalerts.com/lj</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LL</t>
+          <t>https://www.secretstockalerts.com/lk</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LM</t>
+          <t>https://www.secretstockalerts.com/ll</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LN</t>
+          <t>https://www.secretstockalerts.com/lm</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LO</t>
+          <t>https://www.secretstockalerts.com/ln</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LP</t>
+          <t>https://www.secretstockalerts.com/lo</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LQ</t>
+          <t>https://www.secretstockalerts.com/lp</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LR</t>
+          <t>https://www.secretstockalerts.com/lq</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LS</t>
+          <t>https://www.secretstockalerts.com/lr</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LT</t>
+          <t>https://www.secretstockalerts.com/ls</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LU</t>
+          <t>https://www.secretstockalerts.com/lt</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LV</t>
+          <t>https://www.secretstockalerts.com/lu</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LW</t>
+          <t>https://www.secretstockalerts.com/lv</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LX</t>
+          <t>https://www.secretstockalerts.com/lw</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LY</t>
+          <t>https://www.secretstockalerts.com/lx</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/LZ</t>
+          <t>https://www.secretstockalerts.com/ly</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MA</t>
+          <t>https://www.secretstockalerts.com/lz</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MB</t>
+          <t>https://www.secretstockalerts.com/ma</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MC</t>
+          <t>https://www.secretstockalerts.com/mb</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MD</t>
+          <t>https://www.secretstockalerts.com/mc</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ME</t>
+          <t>https://www.secretstockalerts.com/md</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MF</t>
+          <t>https://www.secretstockalerts.com/me</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MG</t>
+          <t>https://www.secretstockalerts.com/mf</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MH</t>
+          <t>https://www.secretstockalerts.com/mg</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MI</t>
+          <t>https://www.secretstockalerts.com/mh</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MJ</t>
+          <t>https://www.secretstockalerts.com/mi</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MK</t>
+          <t>https://www.secretstockalerts.com/mj</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ML</t>
+          <t>https://www.secretstockalerts.com/mk</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MM</t>
+          <t>https://www.secretstockalerts.com/ml</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MN</t>
+          <t>https://www.secretstockalerts.com/mm</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MO</t>
+          <t>https://www.secretstockalerts.com/mn</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MP</t>
+          <t>https://www.secretstockalerts.com/mo</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MQ</t>
+          <t>https://www.secretstockalerts.com/mp</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MR</t>
+          <t>https://www.secretstockalerts.com/mq</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MS</t>
+          <t>https://www.secretstockalerts.com/mr</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MT</t>
+          <t>https://www.secretstockalerts.com/ms</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MU</t>
+          <t>https://www.secretstockalerts.com/mt</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MV</t>
+          <t>https://www.secretstockalerts.com/mu</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MW</t>
+          <t>https://www.secretstockalerts.com/mv</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MX</t>
+          <t>https://www.secretstockalerts.com/mw</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MY</t>
+          <t>https://www.secretstockalerts.com/mx</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/MZ</t>
+          <t>https://www.secretstockalerts.com/my</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NA</t>
+          <t>https://www.secretstockalerts.com/mz</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NB</t>
+          <t>https://www.secretstockalerts.com/na</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NC</t>
+          <t>https://www.secretstockalerts.com/nb</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ND</t>
+          <t>https://www.secretstockalerts.com/nc</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NE</t>
+          <t>https://www.secretstockalerts.com/nd</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NF</t>
+          <t>https://www.secretstockalerts.com/ne</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NG</t>
+          <t>https://www.secretstockalerts.com/nf</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NH</t>
+          <t>https://www.secretstockalerts.com/ng</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NI</t>
+          <t>https://www.secretstockalerts.com/nh</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NJ</t>
+          <t>https://www.secretstockalerts.com/ni</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NK</t>
+          <t>https://www.secretstockalerts.com/nj</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NL</t>
+          <t>https://www.secretstockalerts.com/nk</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NM</t>
+          <t>https://www.secretstockalerts.com/nl</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NN</t>
+          <t>https://www.secretstockalerts.com/nm</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NO</t>
+          <t>https://www.secretstockalerts.com/nn</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NP</t>
+          <t>https://www.secretstockalerts.com/no</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NQ</t>
+          <t>https://www.secretstockalerts.com/np</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NR</t>
+          <t>https://www.secretstockalerts.com/nq</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NS</t>
+          <t>https://www.secretstockalerts.com/nr</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NT</t>
+          <t>https://www.secretstockalerts.com/ns</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NU</t>
+          <t>https://www.secretstockalerts.com/nt</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NV</t>
+          <t>https://www.secretstockalerts.com/nu</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NW</t>
+          <t>https://www.secretstockalerts.com/nv</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NX</t>
+          <t>https://www.secretstockalerts.com/nw</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NY</t>
+          <t>https://www.secretstockalerts.com/nx</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/NZ</t>
+          <t>https://www.secretstockalerts.com/ny</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OA</t>
+          <t>https://www.secretstockalerts.com/nz</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OB</t>
+          <t>https://www.secretstockalerts.com/oa</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OC</t>
+          <t>https://www.secretstockalerts.com/ob</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OD</t>
+          <t>https://www.secretstockalerts.com/oc</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OE</t>
+          <t>https://www.secretstockalerts.com/od</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OF</t>
+          <t>https://www.secretstockalerts.com/oe</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OG</t>
+          <t>https://www.secretstockalerts.com/of</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OH</t>
+          <t>https://www.secretstockalerts.com/og</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OI</t>
+          <t>https://www.secretstockalerts.com/oh</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OJ</t>
+          <t>https://www.secretstockalerts.com/oi</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OK</t>
+          <t>https://www.secretstockalerts.com/oj</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OL</t>
+          <t>https://www.secretstockalerts.com/ok</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OM</t>
+          <t>https://www.secretstockalerts.com/ol</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ON</t>
+          <t>https://www.secretstockalerts.com/om</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OO</t>
+          <t>https://www.secretstockalerts.com/on</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OP</t>
+          <t>https://www.secretstockalerts.com/oo</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OQ</t>
+          <t>https://www.secretstockalerts.com/op</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OR</t>
+          <t>https://www.secretstockalerts.com/oq</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OS</t>
+          <t>https://www.secretstockalerts.com/or</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OT</t>
+          <t>https://www.secretstockalerts.com/os</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OU</t>
+          <t>https://www.secretstockalerts.com/ot</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OV</t>
+          <t>https://www.secretstockalerts.com/ou</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OW</t>
+          <t>https://www.secretstockalerts.com/ov</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OX</t>
+          <t>https://www.secretstockalerts.com/ow</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OY</t>
+          <t>https://www.secretstockalerts.com/ox</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/OZ</t>
+          <t>https://www.secretstockalerts.com/oy</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PA</t>
+          <t>https://www.secretstockalerts.com/oz</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PB</t>
+          <t>https://www.secretstockalerts.com/pa</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PC</t>
+          <t>https://www.secretstockalerts.com/pb</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PD</t>
+          <t>https://www.secretstockalerts.com/pc</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PE</t>
+          <t>https://www.secretstockalerts.com/pd</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PF</t>
+          <t>https://www.secretstockalerts.com/pe</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PG</t>
+          <t>https://www.secretstockalerts.com/pf</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PH</t>
+          <t>https://www.secretstockalerts.com/pg</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PI</t>
+          <t>https://www.secretstockalerts.com/ph</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PJ</t>
+          <t>https://www.secretstockalerts.com/pi</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PK</t>
+          <t>https://www.secretstockalerts.com/pj</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PL</t>
+          <t>https://www.secretstockalerts.com/pk</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PM</t>
+          <t>https://www.secretstockalerts.com/pl</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PN</t>
+          <t>https://www.secretstockalerts.com/pm</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PO</t>
+          <t>https://www.secretstockalerts.com/pn</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PP</t>
+          <t>https://www.secretstockalerts.com/po</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PQ</t>
+          <t>https://www.secretstockalerts.com/pp</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PR</t>
+          <t>https://www.secretstockalerts.com/pq</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PS</t>
+          <t>https://www.secretstockalerts.com/pr</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PT</t>
+          <t>https://www.secretstockalerts.com/ps</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PU</t>
+          <t>https://www.secretstockalerts.com/pt</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PV</t>
+          <t>https://www.secretstockalerts.com/pu</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PW</t>
+          <t>https://www.secretstockalerts.com/pv</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PX</t>
+          <t>https://www.secretstockalerts.com/pw</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PY</t>
+          <t>https://www.secretstockalerts.com/px</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/PZ</t>
+          <t>https://www.secretstockalerts.com/py</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QA</t>
+          <t>https://www.secretstockalerts.com/pz</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QB</t>
+          <t>https://www.secretstockalerts.com/qa</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QC</t>
+          <t>https://www.secretstockalerts.com/qb</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QD</t>
+          <t>https://www.secretstockalerts.com/qc</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QE</t>
+          <t>https://www.secretstockalerts.com/qd</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QF</t>
+          <t>https://www.secretstockalerts.com/qe</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QG</t>
+          <t>https://www.secretstockalerts.com/qf</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QH</t>
+          <t>https://www.secretstockalerts.com/qg</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QI</t>
+          <t>https://www.secretstockalerts.com/qh</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QJ</t>
+          <t>https://www.secretstockalerts.com/qi</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QK</t>
+          <t>https://www.secretstockalerts.com/qj</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QL</t>
+          <t>https://www.secretstockalerts.com/qk</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QM</t>
+          <t>https://www.secretstockalerts.com/ql</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QN</t>
+          <t>https://www.secretstockalerts.com/qm</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QO</t>
+          <t>https://www.secretstockalerts.com/qn</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QP</t>
+          <t>https://www.secretstockalerts.com/qo</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QQ</t>
+          <t>https://www.secretstockalerts.com/qp</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QR</t>
+          <t>https://www.secretstockalerts.com/qq</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QS</t>
+          <t>https://www.secretstockalerts.com/qr</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QT</t>
+          <t>https://www.secretstockalerts.com/qs</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QU</t>
+          <t>https://www.secretstockalerts.com/qt</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QV</t>
+          <t>https://www.secretstockalerts.com/qu</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QW</t>
+          <t>https://www.secretstockalerts.com/qv</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QX</t>
+          <t>https://www.secretstockalerts.com/qw</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QY</t>
+          <t>https://www.secretstockalerts.com/qx</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/QZ</t>
+          <t>https://www.secretstockalerts.com/qy</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RA</t>
+          <t>https://www.secretstockalerts.com/qz</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RB</t>
+          <t>https://www.secretstockalerts.com/ra</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RC</t>
+          <t>https://www.secretstockalerts.com/rb</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RD</t>
+          <t>https://www.secretstockalerts.com/rc</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RE</t>
+          <t>https://www.secretstockalerts.com/rd</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RF</t>
+          <t>https://www.secretstockalerts.com/re</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RG</t>
+          <t>https://www.secretstockalerts.com/rf</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RH</t>
+          <t>https://www.secretstockalerts.com/rg</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RI</t>
+          <t>https://www.secretstockalerts.com/rh</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RJ</t>
+          <t>https://www.secretstockalerts.com/ri</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RK</t>
+          <t>https://www.secretstockalerts.com/rj</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RL</t>
+          <t>https://www.secretstockalerts.com/rk</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RM</t>
+          <t>https://www.secretstockalerts.com/rl</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RN</t>
+          <t>https://www.secretstockalerts.com/rm</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RO</t>
+          <t>https://www.secretstockalerts.com/rn</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RP</t>
+          <t>https://www.secretstockalerts.com/ro</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RQ</t>
+          <t>https://www.secretstockalerts.com/rp</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RR</t>
+          <t>https://www.secretstockalerts.com/rq</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RS</t>
+          <t>https://www.secretstockalerts.com/rr</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RT</t>
+          <t>https://www.secretstockalerts.com/rs</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RU</t>
+          <t>https://www.secretstockalerts.com/rt</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RV</t>
+          <t>https://www.secretstockalerts.com/ru</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RW</t>
+          <t>https://www.secretstockalerts.com/rv</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RX</t>
+          <t>https://www.secretstockalerts.com/rw</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RY</t>
+          <t>https://www.secretstockalerts.com/rx</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/RZ</t>
+          <t>https://www.secretstockalerts.com/ry</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SA</t>
+          <t>https://www.secretstockalerts.com/rz</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SB</t>
+          <t>https://www.secretstockalerts.com/sa</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SC</t>
+          <t>https://www.secretstockalerts.com/sb</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SD</t>
+          <t>https://www.secretstockalerts.com/sc</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SE</t>
+          <t>https://www.secretstockalerts.com/sd</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SF</t>
+          <t>https://www.secretstockalerts.com/se</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SG</t>
+          <t>https://www.secretstockalerts.com/sf</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SH</t>
+          <t>https://www.secretstockalerts.com/sg</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SI</t>
+          <t>https://www.secretstockalerts.com/sh</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SJ</t>
+          <t>https://www.secretstockalerts.com/si</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SK</t>
+          <t>https://www.secretstockalerts.com/sj</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SL</t>
+          <t>https://www.secretstockalerts.com/sk</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SM</t>
+          <t>https://www.secretstockalerts.com/sl</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SN</t>
+          <t>https://www.secretstockalerts.com/sm</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SO</t>
+          <t>https://www.secretstockalerts.com/sn</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SP</t>
+          <t>https://www.secretstockalerts.com/so</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SQ</t>
+          <t>https://www.secretstockalerts.com/sp</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SR</t>
+          <t>https://www.secretstockalerts.com/sq</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SS</t>
+          <t>https://www.secretstockalerts.com/sr</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ST</t>
+          <t>https://www.secretstockalerts.com/ss</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SU</t>
+          <t>https://www.secretstockalerts.com/st</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SV</t>
+          <t>https://www.secretstockalerts.com/su</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SW</t>
+          <t>https://www.secretstockalerts.com/sv</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SX</t>
+          <t>https://www.secretstockalerts.com/sw</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SY</t>
+          <t>https://www.secretstockalerts.com/sx</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/SZ</t>
+          <t>https://www.secretstockalerts.com/sy</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TA</t>
+          <t>https://www.secretstockalerts.com/sz</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TB</t>
+          <t>https://www.secretstockalerts.com/ta</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TC</t>
+          <t>https://www.secretstockalerts.com/tb</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TD</t>
+          <t>https://www.secretstockalerts.com/tc</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TE</t>
+          <t>https://www.secretstockalerts.com/td</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TF</t>
+          <t>https://www.secretstockalerts.com/te</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TG</t>
+          <t>https://www.secretstockalerts.com/tf</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TH</t>
+          <t>https://www.secretstockalerts.com/tg</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TI</t>
+          <t>https://www.secretstockalerts.com/th</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TJ</t>
+          <t>https://www.secretstockalerts.com/ti</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TK</t>
+          <t>https://www.secretstockalerts.com/tj</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TL</t>
+          <t>https://www.secretstockalerts.com/tk</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TM</t>
+          <t>https://www.secretstockalerts.com/tl</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TN</t>
+          <t>https://www.secretstockalerts.com/tm</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TO</t>
+          <t>https://www.secretstockalerts.com/tn</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TP</t>
+          <t>https://www.secretstockalerts.com/to</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TQ</t>
+          <t>https://www.secretstockalerts.com/tp</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TR</t>
+          <t>https://www.secretstockalerts.com/tq</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TS</t>
+          <t>https://www.secretstockalerts.com/tr</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TT</t>
+          <t>https://www.secretstockalerts.com/ts</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TU</t>
+          <t>https://www.secretstockalerts.com/tt</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TV</t>
+          <t>https://www.secretstockalerts.com/tu</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TW</t>
+          <t>https://www.secretstockalerts.com/tv</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TX</t>
+          <t>https://www.secretstockalerts.com/tw</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TY</t>
+          <t>https://www.secretstockalerts.com/tx</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/TZ</t>
+          <t>https://www.secretstockalerts.com/ty</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UA</t>
+          <t>https://www.secretstockalerts.com/tz</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UB</t>
+          <t>https://www.secretstockalerts.com/ua</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UC</t>
+          <t>https://www.secretstockalerts.com/ub</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UD</t>
+          <t>https://www.secretstockalerts.com/uc</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UE</t>
+          <t>https://www.secretstockalerts.com/ud</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UF</t>
+          <t>https://www.secretstockalerts.com/ue</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UG</t>
+          <t>https://www.secretstockalerts.com/uf</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UH</t>
+          <t>https://www.secretstockalerts.com/ug</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UI</t>
+          <t>https://www.secretstockalerts.com/uh</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UJ</t>
+          <t>https://www.secretstockalerts.com/ui</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UK</t>
+          <t>https://www.secretstockalerts.com/uj</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UL</t>
+          <t>https://www.secretstockalerts.com/uk</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UM</t>
+          <t>https://www.secretstockalerts.com/ul</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UN</t>
+          <t>https://www.secretstockalerts.com/um</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UO</t>
+          <t>https://www.secretstockalerts.com/un</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UP</t>
+          <t>https://www.secretstockalerts.com/uo</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UQ</t>
+          <t>https://www.secretstockalerts.com/up</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UR</t>
+          <t>https://www.secretstockalerts.com/uq</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/US</t>
+          <t>https://www.secretstockalerts.com/ur</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UT</t>
+          <t>https://www.secretstockalerts.com/us</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UU</t>
+          <t>https://www.secretstockalerts.com/ut</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UV</t>
+          <t>https://www.secretstockalerts.com/uu</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UW</t>
+          <t>https://www.secretstockalerts.com/uv</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UX</t>
+          <t>https://www.secretstockalerts.com/uw</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UY</t>
+          <t>https://www.secretstockalerts.com/ux</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/UZ</t>
+          <t>https://www.secretstockalerts.com/uy</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VA</t>
+          <t>https://www.secretstockalerts.com/uz</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VB</t>
+          <t>https://www.secretstockalerts.com/va</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VC</t>
+          <t>https://www.secretstockalerts.com/vb</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VD</t>
+          <t>https://www.secretstockalerts.com/vc</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VE</t>
+          <t>https://www.secretstockalerts.com/vd</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VF</t>
+          <t>https://www.secretstockalerts.com/ve</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VG</t>
+          <t>https://www.secretstockalerts.com/vf</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VH</t>
+          <t>https://www.secretstockalerts.com/vg</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VI</t>
+          <t>https://www.secretstockalerts.com/vh</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VJ</t>
+          <t>https://www.secretstockalerts.com/vi</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VK</t>
+          <t>https://www.secretstockalerts.com/vj</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VL</t>
+          <t>https://www.secretstockalerts.com/vk</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VM</t>
+          <t>https://www.secretstockalerts.com/vl</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VN</t>
+          <t>https://www.secretstockalerts.com/vm</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VO</t>
+          <t>https://www.secretstockalerts.com/vn</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VP</t>
+          <t>https://www.secretstockalerts.com/vo</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VQ</t>
+          <t>https://www.secretstockalerts.com/vp</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VR</t>
+          <t>https://www.secretstockalerts.com/vq</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VS</t>
+          <t>https://www.secretstockalerts.com/vr</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VT</t>
+          <t>https://www.secretstockalerts.com/vs</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VU</t>
+          <t>https://www.secretstockalerts.com/vt</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VV</t>
+          <t>https://www.secretstockalerts.com/vu</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VW</t>
+          <t>https://www.secretstockalerts.com/vv</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VX</t>
+          <t>https://www.secretstockalerts.com/vw</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VY</t>
+          <t>https://www.secretstockalerts.com/vx</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/VZ</t>
+          <t>https://www.secretstockalerts.com/vy</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WA</t>
+          <t>https://www.secretstockalerts.com/vz</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WB</t>
+          <t>https://www.secretstockalerts.com/wa</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WC</t>
+          <t>https://www.secretstockalerts.com/wb</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WD</t>
+          <t>https://www.secretstockalerts.com/wc</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WE</t>
+          <t>https://www.secretstockalerts.com/wd</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WF</t>
+          <t>https://www.secretstockalerts.com/we</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WG</t>
+          <t>https://www.secretstockalerts.com/wf</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WH</t>
+          <t>https://www.secretstockalerts.com/wg</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WI</t>
+          <t>https://www.secretstockalerts.com/wh</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WJ</t>
+          <t>https://www.secretstockalerts.com/wi</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WK</t>
+          <t>https://www.secretstockalerts.com/wj</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WL</t>
+          <t>https://www.secretstockalerts.com/wk</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WM</t>
+          <t>https://www.secretstockalerts.com/wl</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WN</t>
+          <t>https://www.secretstockalerts.com/wm</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WO</t>
+          <t>https://www.secretstockalerts.com/wn</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WP</t>
+          <t>https://www.secretstockalerts.com/wo</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WQ</t>
+          <t>https://www.secretstockalerts.com/wp</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WR</t>
+          <t>https://www.secretstockalerts.com/wq</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WS</t>
+          <t>https://www.secretstockalerts.com/wr</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WT</t>
+          <t>https://www.secretstockalerts.com/ws</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WU</t>
+          <t>https://www.secretstockalerts.com/wt</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WV</t>
+          <t>https://www.secretstockalerts.com/wu</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WW</t>
+          <t>https://www.secretstockalerts.com/wv</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WX</t>
+          <t>https://www.secretstockalerts.com/ww</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WY</t>
+          <t>https://www.secretstockalerts.com/wx</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/WZ</t>
+          <t>https://www.secretstockalerts.com/wy</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XA</t>
+          <t>https://www.secretstockalerts.com/wz</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XB</t>
+          <t>https://www.secretstockalerts.com/xa</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XC</t>
+          <t>https://www.secretstockalerts.com/xb</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XD</t>
+          <t>https://www.secretstockalerts.com/xc</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XE</t>
+          <t>https://www.secretstockalerts.com/xd</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XF</t>
+          <t>https://www.secretstockalerts.com/xe</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XG</t>
+          <t>https://www.secretstockalerts.com/xf</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XH</t>
+          <t>https://www.secretstockalerts.com/xg</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XI</t>
+          <t>https://www.secretstockalerts.com/xh</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XJ</t>
+          <t>https://www.secretstockalerts.com/xi</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XK</t>
+          <t>https://www.secretstockalerts.com/xj</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XL</t>
+          <t>https://www.secretstockalerts.com/xk</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XM</t>
+          <t>https://www.secretstockalerts.com/xl</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XN</t>
+          <t>https://www.secretstockalerts.com/xm</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XO</t>
+          <t>https://www.secretstockalerts.com/xn</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XP</t>
+          <t>https://www.secretstockalerts.com/xo</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XQ</t>
+          <t>https://www.secretstockalerts.com/xp</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XR</t>
+          <t>https://www.secretstockalerts.com/xq</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XS</t>
+          <t>https://www.secretstockalerts.com/xr</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XT</t>
+          <t>https://www.secretstockalerts.com/xs</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XU</t>
+          <t>https://www.secretstockalerts.com/xt</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XV</t>
+          <t>https://www.secretstockalerts.com/xu</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XW</t>
+          <t>https://www.secretstockalerts.com/xv</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XX</t>
+          <t>https://www.secretstockalerts.com/xw</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XY</t>
+          <t>https://www.secretstockalerts.com/xx</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/XZ</t>
+          <t>https://www.secretstockalerts.com/xy</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YA</t>
+          <t>https://www.secretstockalerts.com/xz</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YB</t>
+          <t>https://www.secretstockalerts.com/ya</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YC</t>
+          <t>https://www.secretstockalerts.com/yb</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YD</t>
+          <t>https://www.secretstockalerts.com/yc</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YE</t>
+          <t>https://www.secretstockalerts.com/yd</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YF</t>
+          <t>https://www.secretstockalerts.com/ye</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YG</t>
+          <t>https://www.secretstockalerts.com/yf</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YH</t>
+          <t>https://www.secretstockalerts.com/yg</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YI</t>
+          <t>https://www.secretstockalerts.com/yh</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YJ</t>
+          <t>https://www.secretstockalerts.com/yi</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YK</t>
+          <t>https://www.secretstockalerts.com/yj</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YL</t>
+          <t>https://www.secretstockalerts.com/yk</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YM</t>
+          <t>https://www.secretstockalerts.com/yl</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YN</t>
+          <t>https://www.secretstockalerts.com/ym</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YO</t>
+          <t>https://www.secretstockalerts.com/yn</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YP</t>
+          <t>https://www.secretstockalerts.com/yo</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YQ</t>
+          <t>https://www.secretstockalerts.com/yp</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YR</t>
+          <t>https://www.secretstockalerts.com/yq</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YS</t>
+          <t>https://www.secretstockalerts.com/yr</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YT</t>
+          <t>https://www.secretstockalerts.com/ys</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YU</t>
+          <t>https://www.secretstockalerts.com/yt</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YV</t>
+          <t>https://www.secretstockalerts.com/yu</t>
         </is>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YW</t>
+          <t>https://www.secretstockalerts.com/yv</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YX</t>
+          <t>https://www.secretstockalerts.com/yw</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YY</t>
+          <t>https://www.secretstockalerts.com/yx</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/YZ</t>
+          <t>https://www.secretstockalerts.com/yy</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZA</t>
+          <t>https://www.secretstockalerts.com/yz</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZB</t>
+          <t>https://www.secretstockalerts.com/za</t>
         </is>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZC</t>
+          <t>https://www.secretstockalerts.com/zb</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZD</t>
+          <t>https://www.secretstockalerts.com/zc</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZE</t>
+          <t>https://www.secretstockalerts.com/zd</t>
         </is>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZF</t>
+          <t>https://www.secretstockalerts.com/ze</t>
         </is>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZG</t>
+          <t>https://www.secretstockalerts.com/zf</t>
         </is>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZH</t>
+          <t>https://www.secretstockalerts.com/zg</t>
         </is>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZI</t>
+          <t>https://www.secretstockalerts.com/zh</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZJ</t>
+          <t>https://www.secretstockalerts.com/zi</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZK</t>
+          <t>https://www.secretstockalerts.com/zj</t>
         </is>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZL</t>
+          <t>https://www.secretstockalerts.com/zk</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZM</t>
+          <t>https://www.secretstockalerts.com/zl</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZN</t>
+          <t>https://www.secretstockalerts.com/zm</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZO</t>
+          <t>https://www.secretstockalerts.com/zn</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZP</t>
+          <t>https://www.secretstockalerts.com/zo</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZQ</t>
+          <t>https://www.secretstockalerts.com/zp</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZR</t>
+          <t>https://www.secretstockalerts.com/zq</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZS</t>
+          <t>https://www.secretstockalerts.com/zr</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZT</t>
+          <t>https://www.secretstockalerts.com/zs</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZU</t>
+          <t>https://www.secretstockalerts.com/zt</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZV</t>
+          <t>https://www.secretstockalerts.com/zu</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZW</t>
+          <t>https://www.secretstockalerts.com/zv</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZX</t>
+          <t>https://www.secretstockalerts.com/zw</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZY</t>
+          <t>https://www.secretstockalerts.com/zx</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>https://www.secretstockalerts.com/ZZ</t>
+          <t>https://www.secretstockalerts.com/zy</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>https://www.secretstockalerts.com/zz</t>
         </is>
       </c>
     </row>
